--- a/PROJECT MAOLIN/Miaolin Customer test.xlsx
+++ b/PROJECT MAOLIN/Miaolin Customer test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\web\craveva-staging\PROJECT MAOLIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D013873-E1ED-45F3-ACAA-BA3463ED7658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515F620F-D273-4716-B3A7-45AB90A99EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E75082F1-4D03-491B-90C2-F0E6D26CBA86}"/>
   </bookViews>

--- a/PROJECT MAOLIN/Miaolin Customer test.xlsx
+++ b/PROJECT MAOLIN/Miaolin Customer test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\web\craveva-staging\PROJECT MAOLIN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\web\craveva-staging\PROJECT MAOLIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8035517E-8BE5-4844-AF18-56B3D3A12FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C87602-C464-4AF3-A205-693151CF92E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E75082F1-4D03-491B-90C2-F0E6D26CBA86}"/>
   </bookViews>
